--- a/public/sample_uploads/investments.xlsx
+++ b/public/sample_uploads/investments.xlsx
@@ -41,10 +41,10 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Mandatory in dd/mm/yyyy format</t>
+          <t xml:space="preserve">Optional, Input investment ID if you intend to update an existing investment</t>
         </r>
       </text>
     </comment>
@@ -57,6 +57,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Author:
+-Mandatory
 </t>
         </r>
         <r>
@@ -64,11 +65,10 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">-Investor name as recorded on CapHive is mandatory incase account entry pertains to a specific investor
--Leave blank incase account entry pertains to a fund / scheme</t>
+          <t xml:space="preserve">-Investor name as recorded on CapHive</t>
         </r>
       </text>
     </comment>
@@ -80,18 +80,9 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Mandatory: Fund name recorded on CapHive</t>
+          <t xml:space="preserve">Author: 
+-Mandatory
+-Either of Founder,  Employee, Other, Self ( For funds own investments in the Portco)</t>
         </r>
       </text>
     </comment>
@@ -104,18 +95,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Mandatory, needed for mapping to the appropriate folio.  
-If needed you may download the list of commiments which will give the Investor Name and Folio No.</t>
+-Mandatory
+- Currency of the investment</t>
         </r>
       </text>
     </comment>
@@ -128,17 +109,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Mandatory in dd/mm/yyyy format</t>
+Name of the investing parties</t>
         </r>
       </text>
     </comment>
@@ -151,18 +122,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">-Mandatory 
--Please use the existing nomenclature as shown by CapHive</t>
+-Optional
+- Add classifications to the categories, For eg Institutional, Angel etc under Others</t>
         </r>
       </text>
     </comment>
@@ -182,11 +143,11 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">-Mandatory 
--Please use the existing nomenclature as shown by CapHive</t>
+-Either Equity or Convertible</t>
         </r>
       </text>
     </comment>
@@ -206,11 +167,11 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">-Mandatory
--Incase of a percentage - please put the exact value i.e. 0.06 for 6%</t>
+          <t xml:space="preserve">-Mandatory 
+-Name of the round of the investment</t>
         </r>
       </text>
     </comment>
@@ -230,10 +191,11 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Leave blank if you want the system to convert based on FX rates entered by you in the system</t>
+          <t xml:space="preserve">-Mandatory
+-In case the investment type in convertible, enter the fully diluted quantity</t>
         </r>
       </text>
     </comment>
@@ -246,17 +208,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Author:
-</t>
+-</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">-Optional</t>
+          <t xml:space="preserve">Enter the Name of the instrument if the investment type is convertible. 
+-Leave blank if Equity</t>
         </r>
       </text>
     </comment>
@@ -269,17 +232,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Mandatory in dd/mm/yyyy format</t>
+-Quantity of the instrument if the investment type is convertible
+- Leave blank if equity</t>
         </r>
       </text>
     </comment>
@@ -292,18 +246,8 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">-Mandatory
--Please use the existing nomenclature as shown by CapHive</t>
+-Mandatory
+-Enter the per unit price</t>
         </r>
       </text>
     </comment>
@@ -323,7 +267,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Mandatory in dd/mm/yyyy format</t>
@@ -346,10 +290,51 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Mandatory in dd/mm/yyyy format</t>
+          <t xml:space="preserve">-Optional</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Author:
+-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Mandatory
+-Yes if you want to update details of an existing investment
+-No if it is a new investment</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Author:
+-Optional
+-Use this to create custom fields for every investment. 
+-Add a new column for every custom field
+-Delete the column if you do not wish to use this</t>
         </r>
       </text>
     </comment>
@@ -358,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t xml:space="preserve">Id</t>
   </si>
@@ -375,6 +360,9 @@
     <t xml:space="preserve">Investor Name *</t>
   </si>
   <si>
+    <t xml:space="preserve">SubGroup</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investment Type *</t>
   </si>
   <si>
@@ -384,7 +372,10 @@
     <t xml:space="preserve">Quantity *</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount (Folio Currency)</t>
+    <t xml:space="preserve">Instrument Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrument Quantity</t>
   </si>
   <si>
     <t xml:space="preserve">Price *</t>
@@ -402,7 +393,7 @@
     <t xml:space="preserve">Custom Field 1</t>
   </si>
   <si>
-    <t xml:space="preserve">F Pvt Ltd</t>
+    <t xml:space="preserve">AX</t>
   </si>
   <si>
     <t xml:space="preserve">Founder</t>
@@ -411,13 +402,13 @@
     <t xml:space="preserve">USD</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Inv 1</t>
+    <t xml:space="preserve">John Doe</t>
   </si>
   <si>
-    <t xml:space="preserve">Convertible</t>
+    <t xml:space="preserve">Equity</t>
   </si>
   <si>
-    <t xml:space="preserve">A</t>
+    <t xml:space="preserve">Founding</t>
   </si>
   <si>
     <t xml:space="preserve">12/05/2025</t>
@@ -429,22 +420,25 @@
     <t xml:space="preserve">Old</t>
   </si>
   <si>
-    <t xml:space="preserve">Employee</t>
+    <t xml:space="preserve">Other</t>
   </si>
   <si>
-    <t xml:space="preserve">INR</t>
+    <t xml:space="preserve">NorthInc Ventures</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Inv 2</t>
+    <t xml:space="preserve">Institutional</t>
   </si>
   <si>
-    <t xml:space="preserve">Equity</t>
+    <t xml:space="preserve">Convertible</t>
   </si>
   <si>
-    <t xml:space="preserve">B</t>
+    <t xml:space="preserve">Series A</t>
   </si>
   <si>
-    <t xml:space="preserve">15/02/2025</t>
+    <t xml:space="preserve">CCPS Series A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">New</t>
@@ -516,7 +510,7 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -602,12 +596,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -803,23 +797,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:P1003"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.53"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="22.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="9.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16366" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="15.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="23.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="22.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="9.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="15.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16368" style="1" width="10.18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -865,81 +860,4104 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
+      <c r="L3" s="1" t="n">
+        <v>10000</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
+      <c r="M3" s="5" t="s">
+        <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="O3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
+      <c r="P3" s="4" t="s">
+        <v>32</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>29</v>
-      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="4"/>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="4"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="4"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="4"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="4"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="4"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="4"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="4"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="4"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="4"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="4"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="4"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="4"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="4"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="4"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="4"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="4"/>
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="4"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="4"/>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="4"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="4"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="4"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="4"/>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="4"/>
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="4"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="4"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="4"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="4"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="4"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="4"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="4"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="4"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="4"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="4"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C38" s="4"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C39" s="4"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="4"/>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="4"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C42" s="4"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="4"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C44" s="4"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C45" s="4"/>
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C46" s="4"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C47" s="4"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C48" s="4"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C49" s="4"/>
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C50" s="4"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C51" s="4"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C52" s="4"/>
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C53" s="4"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C54" s="4"/>
+      <c r="O54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C55" s="4"/>
+      <c r="O55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C56" s="4"/>
+      <c r="O56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C57" s="4"/>
+      <c r="O57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C58" s="4"/>
+      <c r="O58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C59" s="4"/>
+      <c r="O59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="4"/>
+      <c r="O60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C61" s="4"/>
+      <c r="O61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C62" s="4"/>
+      <c r="O62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C63" s="4"/>
+      <c r="O63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="4"/>
+      <c r="O64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C65" s="4"/>
+      <c r="O65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C66" s="4"/>
+      <c r="O66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C67" s="4"/>
+      <c r="O67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C68" s="4"/>
+      <c r="O68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C69" s="4"/>
+      <c r="O69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C70" s="4"/>
+      <c r="O70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C71" s="4"/>
+      <c r="O71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="4"/>
+      <c r="O72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C73" s="4"/>
+      <c r="O73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C74" s="4"/>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="4"/>
+      <c r="O75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C76" s="4"/>
+      <c r="O76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C77" s="4"/>
+      <c r="O77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="4"/>
+      <c r="O78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="4"/>
+      <c r="O79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C80" s="4"/>
+      <c r="O80" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C81" s="4"/>
+      <c r="O81" s="4"/>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="4"/>
+      <c r="O82" s="4"/>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C83" s="4"/>
+      <c r="O83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C84" s="4"/>
+      <c r="O84" s="4"/>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C85" s="4"/>
+      <c r="O85" s="4"/>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C86" s="4"/>
+      <c r="O86" s="4"/>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="4"/>
+      <c r="O87" s="4"/>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C88" s="4"/>
+      <c r="O88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C89" s="4"/>
+      <c r="O89" s="4"/>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C90" s="4"/>
+      <c r="O90" s="4"/>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C91" s="4"/>
+      <c r="O91" s="4"/>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C92" s="4"/>
+      <c r="O92" s="4"/>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C93" s="4"/>
+      <c r="O93" s="4"/>
+    </row>
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C94" s="4"/>
+      <c r="O94" s="4"/>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C95" s="4"/>
+      <c r="O95" s="4"/>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C96" s="4"/>
+      <c r="O96" s="4"/>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C97" s="4"/>
+      <c r="O97" s="4"/>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="4"/>
+      <c r="O98" s="4"/>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C99" s="4"/>
+      <c r="O99" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="4"/>
+      <c r="O100" s="4"/>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C101" s="4"/>
+      <c r="O101" s="4"/>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C102" s="4"/>
+      <c r="O102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C103" s="4"/>
+      <c r="O103" s="4"/>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C104" s="4"/>
+      <c r="O104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="4"/>
+      <c r="O105" s="4"/>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="4"/>
+      <c r="O106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C107" s="4"/>
+      <c r="O107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="4"/>
+      <c r="O108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="4"/>
+      <c r="O109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="4"/>
+      <c r="O110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="4"/>
+      <c r="O111" s="4"/>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C112" s="4"/>
+      <c r="O112" s="4"/>
+    </row>
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C113" s="4"/>
+      <c r="O113" s="4"/>
+    </row>
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C114" s="4"/>
+      <c r="O114" s="4"/>
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="4"/>
+      <c r="O115" s="4"/>
+    </row>
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C116" s="4"/>
+      <c r="O116" s="4"/>
+    </row>
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="4"/>
+      <c r="O117" s="4"/>
+    </row>
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C118" s="4"/>
+      <c r="O118" s="4"/>
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="4"/>
+      <c r="O119" s="4"/>
+    </row>
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="4"/>
+      <c r="O120" s="4"/>
+    </row>
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C121" s="4"/>
+      <c r="O121" s="4"/>
+    </row>
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C122" s="4"/>
+      <c r="O122" s="4"/>
+    </row>
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="4"/>
+      <c r="O123" s="4"/>
+    </row>
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C124" s="4"/>
+      <c r="O124" s="4"/>
+    </row>
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C125" s="4"/>
+      <c r="O125" s="4"/>
+    </row>
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C126" s="4"/>
+      <c r="O126" s="4"/>
+    </row>
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C127" s="4"/>
+      <c r="O127" s="4"/>
+    </row>
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C128" s="4"/>
+      <c r="O128" s="4"/>
+    </row>
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C129" s="4"/>
+      <c r="O129" s="4"/>
+    </row>
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C130" s="4"/>
+      <c r="O130" s="4"/>
+    </row>
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C131" s="4"/>
+      <c r="O131" s="4"/>
+    </row>
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C132" s="4"/>
+      <c r="O132" s="4"/>
+    </row>
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C133" s="4"/>
+      <c r="O133" s="4"/>
+    </row>
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C134" s="4"/>
+      <c r="O134" s="4"/>
+    </row>
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C135" s="4"/>
+      <c r="O135" s="4"/>
+    </row>
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C136" s="4"/>
+      <c r="O136" s="4"/>
+    </row>
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C137" s="4"/>
+      <c r="O137" s="4"/>
+    </row>
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C138" s="4"/>
+      <c r="O138" s="4"/>
+    </row>
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C139" s="4"/>
+      <c r="O139" s="4"/>
+    </row>
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C140" s="4"/>
+      <c r="O140" s="4"/>
+    </row>
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C141" s="4"/>
+      <c r="O141" s="4"/>
+    </row>
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C142" s="4"/>
+      <c r="O142" s="4"/>
+    </row>
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C143" s="4"/>
+      <c r="O143" s="4"/>
+    </row>
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C144" s="4"/>
+      <c r="O144" s="4"/>
+    </row>
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C145" s="4"/>
+      <c r="O145" s="4"/>
+    </row>
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C146" s="4"/>
+      <c r="O146" s="4"/>
+    </row>
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C147" s="4"/>
+      <c r="O147" s="4"/>
+    </row>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C148" s="4"/>
+      <c r="O148" s="4"/>
+    </row>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C149" s="4"/>
+      <c r="O149" s="4"/>
+    </row>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C150" s="4"/>
+      <c r="O150" s="4"/>
+    </row>
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C151" s="4"/>
+      <c r="O151" s="4"/>
+    </row>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C152" s="4"/>
+      <c r="O152" s="4"/>
+    </row>
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C153" s="4"/>
+      <c r="O153" s="4"/>
+    </row>
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C154" s="4"/>
+      <c r="O154" s="4"/>
+    </row>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C155" s="4"/>
+      <c r="O155" s="4"/>
+    </row>
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C156" s="4"/>
+      <c r="O156" s="4"/>
+    </row>
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C157" s="4"/>
+      <c r="O157" s="4"/>
+    </row>
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C158" s="4"/>
+      <c r="O158" s="4"/>
+    </row>
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C159" s="4"/>
+      <c r="O159" s="4"/>
+    </row>
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C160" s="4"/>
+      <c r="O160" s="4"/>
+    </row>
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C161" s="4"/>
+      <c r="O161" s="4"/>
+    </row>
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C162" s="4"/>
+      <c r="O162" s="4"/>
+    </row>
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C163" s="4"/>
+      <c r="O163" s="4"/>
+    </row>
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C164" s="4"/>
+      <c r="O164" s="4"/>
+    </row>
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C165" s="4"/>
+      <c r="O165" s="4"/>
+    </row>
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C166" s="4"/>
+      <c r="O166" s="4"/>
+    </row>
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C167" s="4"/>
+      <c r="O167" s="4"/>
+    </row>
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C168" s="4"/>
+      <c r="O168" s="4"/>
+    </row>
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C169" s="4"/>
+      <c r="O169" s="4"/>
+    </row>
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C170" s="4"/>
+      <c r="O170" s="4"/>
+    </row>
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C171" s="4"/>
+      <c r="O171" s="4"/>
+    </row>
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C172" s="4"/>
+      <c r="O172" s="4"/>
+    </row>
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C173" s="4"/>
+      <c r="O173" s="4"/>
+    </row>
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C174" s="4"/>
+      <c r="O174" s="4"/>
+    </row>
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C175" s="4"/>
+      <c r="O175" s="4"/>
+    </row>
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C176" s="4"/>
+      <c r="O176" s="4"/>
+    </row>
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C177" s="4"/>
+      <c r="O177" s="4"/>
+    </row>
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C178" s="4"/>
+      <c r="O178" s="4"/>
+    </row>
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C179" s="4"/>
+      <c r="O179" s="4"/>
+    </row>
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C180" s="4"/>
+      <c r="O180" s="4"/>
+    </row>
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C181" s="4"/>
+      <c r="O181" s="4"/>
+    </row>
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C182" s="4"/>
+      <c r="O182" s="4"/>
+    </row>
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C183" s="4"/>
+      <c r="O183" s="4"/>
+    </row>
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C184" s="4"/>
+      <c r="O184" s="4"/>
+    </row>
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C185" s="4"/>
+      <c r="O185" s="4"/>
+    </row>
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C186" s="4"/>
+      <c r="O186" s="4"/>
+    </row>
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C187" s="4"/>
+      <c r="O187" s="4"/>
+    </row>
+    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C188" s="4"/>
+      <c r="O188" s="4"/>
+    </row>
+    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C189" s="4"/>
+      <c r="O189" s="4"/>
+    </row>
+    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C190" s="4"/>
+      <c r="O190" s="4"/>
+    </row>
+    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C191" s="4"/>
+      <c r="O191" s="4"/>
+    </row>
+    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C192" s="4"/>
+      <c r="O192" s="4"/>
+    </row>
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C193" s="4"/>
+      <c r="O193" s="4"/>
+    </row>
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C194" s="4"/>
+      <c r="O194" s="4"/>
+    </row>
+    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C195" s="4"/>
+      <c r="O195" s="4"/>
+    </row>
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C196" s="4"/>
+      <c r="O196" s="4"/>
+    </row>
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C197" s="4"/>
+      <c r="O197" s="4"/>
+    </row>
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C198" s="4"/>
+      <c r="O198" s="4"/>
+    </row>
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C199" s="4"/>
+      <c r="O199" s="4"/>
+    </row>
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C200" s="4"/>
+      <c r="O200" s="4"/>
+    </row>
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C201" s="4"/>
+      <c r="O201" s="4"/>
+    </row>
+    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C202" s="4"/>
+      <c r="O202" s="4"/>
+    </row>
+    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C203" s="4"/>
+      <c r="O203" s="4"/>
+    </row>
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C204" s="4"/>
+      <c r="O204" s="4"/>
+    </row>
+    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C205" s="4"/>
+      <c r="O205" s="4"/>
+    </row>
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C206" s="4"/>
+      <c r="O206" s="4"/>
+    </row>
+    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C207" s="4"/>
+      <c r="O207" s="4"/>
+    </row>
+    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C208" s="4"/>
+      <c r="O208" s="4"/>
+    </row>
+    <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C209" s="4"/>
+      <c r="O209" s="4"/>
+    </row>
+    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C210" s="4"/>
+      <c r="O210" s="4"/>
+    </row>
+    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C211" s="4"/>
+      <c r="O211" s="4"/>
+    </row>
+    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C212" s="4"/>
+      <c r="O212" s="4"/>
+    </row>
+    <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C213" s="4"/>
+      <c r="O213" s="4"/>
+    </row>
+    <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C214" s="4"/>
+      <c r="O214" s="4"/>
+    </row>
+    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C215" s="4"/>
+      <c r="O215" s="4"/>
+    </row>
+    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C216" s="4"/>
+      <c r="O216" s="4"/>
+    </row>
+    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C217" s="4"/>
+      <c r="O217" s="4"/>
+    </row>
+    <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C218" s="4"/>
+      <c r="O218" s="4"/>
+    </row>
+    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C219" s="4"/>
+      <c r="O219" s="4"/>
+    </row>
+    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C220" s="4"/>
+      <c r="O220" s="4"/>
+    </row>
+    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C221" s="4"/>
+      <c r="O221" s="4"/>
+    </row>
+    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C222" s="4"/>
+      <c r="O222" s="4"/>
+    </row>
+    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C223" s="4"/>
+      <c r="O223" s="4"/>
+    </row>
+    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C224" s="4"/>
+      <c r="O224" s="4"/>
+    </row>
+    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C225" s="4"/>
+      <c r="O225" s="4"/>
+    </row>
+    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C226" s="4"/>
+      <c r="O226" s="4"/>
+    </row>
+    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C227" s="4"/>
+      <c r="O227" s="4"/>
+    </row>
+    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C228" s="4"/>
+      <c r="O228" s="4"/>
+    </row>
+    <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C229" s="4"/>
+      <c r="O229" s="4"/>
+    </row>
+    <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C230" s="4"/>
+      <c r="O230" s="4"/>
+    </row>
+    <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C231" s="4"/>
+      <c r="O231" s="4"/>
+    </row>
+    <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C232" s="4"/>
+      <c r="O232" s="4"/>
+    </row>
+    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C233" s="4"/>
+      <c r="O233" s="4"/>
+    </row>
+    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C234" s="4"/>
+      <c r="O234" s="4"/>
+    </row>
+    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C235" s="4"/>
+      <c r="O235" s="4"/>
+    </row>
+    <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C236" s="4"/>
+      <c r="O236" s="4"/>
+    </row>
+    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C237" s="4"/>
+      <c r="O237" s="4"/>
+    </row>
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C238" s="4"/>
+      <c r="O238" s="4"/>
+    </row>
+    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C239" s="4"/>
+      <c r="O239" s="4"/>
+    </row>
+    <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C240" s="4"/>
+      <c r="O240" s="4"/>
+    </row>
+    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C241" s="4"/>
+      <c r="O241" s="4"/>
+    </row>
+    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C242" s="4"/>
+      <c r="O242" s="4"/>
+    </row>
+    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C243" s="4"/>
+      <c r="O243" s="4"/>
+    </row>
+    <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C244" s="4"/>
+      <c r="O244" s="4"/>
+    </row>
+    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C245" s="4"/>
+      <c r="O245" s="4"/>
+    </row>
+    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C246" s="4"/>
+      <c r="O246" s="4"/>
+    </row>
+    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C247" s="4"/>
+      <c r="O247" s="4"/>
+    </row>
+    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C248" s="4"/>
+      <c r="O248" s="4"/>
+    </row>
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C249" s="4"/>
+      <c r="O249" s="4"/>
+    </row>
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C250" s="4"/>
+      <c r="O250" s="4"/>
+    </row>
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C251" s="4"/>
+      <c r="O251" s="4"/>
+    </row>
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C252" s="4"/>
+      <c r="O252" s="4"/>
+    </row>
+    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C253" s="4"/>
+      <c r="O253" s="4"/>
+    </row>
+    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C254" s="4"/>
+      <c r="O254" s="4"/>
+    </row>
+    <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C255" s="4"/>
+      <c r="O255" s="4"/>
+    </row>
+    <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C256" s="4"/>
+      <c r="O256" s="4"/>
+    </row>
+    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C257" s="4"/>
+      <c r="O257" s="4"/>
+    </row>
+    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C258" s="4"/>
+      <c r="O258" s="4"/>
+    </row>
+    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C259" s="4"/>
+      <c r="O259" s="4"/>
+    </row>
+    <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C260" s="4"/>
+      <c r="O260" s="4"/>
+    </row>
+    <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C261" s="4"/>
+      <c r="O261" s="4"/>
+    </row>
+    <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C262" s="4"/>
+      <c r="O262" s="4"/>
+    </row>
+    <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C263" s="4"/>
+      <c r="O263" s="4"/>
+    </row>
+    <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C264" s="4"/>
+      <c r="O264" s="4"/>
+    </row>
+    <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C265" s="4"/>
+      <c r="O265" s="4"/>
+    </row>
+    <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C266" s="4"/>
+      <c r="O266" s="4"/>
+    </row>
+    <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C267" s="4"/>
+      <c r="O267" s="4"/>
+    </row>
+    <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C268" s="4"/>
+      <c r="O268" s="4"/>
+    </row>
+    <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C269" s="4"/>
+      <c r="O269" s="4"/>
+    </row>
+    <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C270" s="4"/>
+      <c r="O270" s="4"/>
+    </row>
+    <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C271" s="4"/>
+      <c r="O271" s="4"/>
+    </row>
+    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C272" s="4"/>
+      <c r="O272" s="4"/>
+    </row>
+    <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C273" s="4"/>
+      <c r="O273" s="4"/>
+    </row>
+    <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C274" s="4"/>
+      <c r="O274" s="4"/>
+    </row>
+    <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C275" s="4"/>
+      <c r="O275" s="4"/>
+    </row>
+    <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C276" s="4"/>
+      <c r="O276" s="4"/>
+    </row>
+    <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C277" s="4"/>
+      <c r="O277" s="4"/>
+    </row>
+    <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C278" s="4"/>
+      <c r="O278" s="4"/>
+    </row>
+    <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C279" s="4"/>
+      <c r="O279" s="4"/>
+    </row>
+    <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C280" s="4"/>
+      <c r="O280" s="4"/>
+    </row>
+    <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C281" s="4"/>
+      <c r="O281" s="4"/>
+    </row>
+    <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C282" s="4"/>
+      <c r="O282" s="4"/>
+    </row>
+    <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C283" s="4"/>
+      <c r="O283" s="4"/>
+    </row>
+    <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C284" s="4"/>
+      <c r="O284" s="4"/>
+    </row>
+    <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C285" s="4"/>
+      <c r="O285" s="4"/>
+    </row>
+    <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C286" s="4"/>
+      <c r="O286" s="4"/>
+    </row>
+    <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C287" s="4"/>
+      <c r="O287" s="4"/>
+    </row>
+    <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C288" s="4"/>
+      <c r="O288" s="4"/>
+    </row>
+    <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C289" s="4"/>
+      <c r="O289" s="4"/>
+    </row>
+    <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C290" s="4"/>
+      <c r="O290" s="4"/>
+    </row>
+    <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C291" s="4"/>
+      <c r="O291" s="4"/>
+    </row>
+    <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C292" s="4"/>
+      <c r="O292" s="4"/>
+    </row>
+    <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C293" s="4"/>
+      <c r="O293" s="4"/>
+    </row>
+    <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C294" s="4"/>
+      <c r="O294" s="4"/>
+    </row>
+    <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C295" s="4"/>
+      <c r="O295" s="4"/>
+    </row>
+    <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C296" s="4"/>
+      <c r="O296" s="4"/>
+    </row>
+    <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C297" s="4"/>
+      <c r="O297" s="4"/>
+    </row>
+    <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C298" s="4"/>
+      <c r="O298" s="4"/>
+    </row>
+    <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C299" s="4"/>
+      <c r="O299" s="4"/>
+    </row>
+    <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C300" s="4"/>
+      <c r="O300" s="4"/>
+    </row>
+    <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C301" s="4"/>
+      <c r="O301" s="4"/>
+    </row>
+    <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C302" s="4"/>
+      <c r="O302" s="4"/>
+    </row>
+    <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C303" s="4"/>
+      <c r="O303" s="4"/>
+    </row>
+    <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C304" s="4"/>
+      <c r="O304" s="4"/>
+    </row>
+    <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C305" s="4"/>
+      <c r="O305" s="4"/>
+    </row>
+    <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C306" s="4"/>
+      <c r="O306" s="4"/>
+    </row>
+    <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C307" s="4"/>
+      <c r="O307" s="4"/>
+    </row>
+    <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C308" s="4"/>
+      <c r="O308" s="4"/>
+    </row>
+    <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C309" s="4"/>
+      <c r="O309" s="4"/>
+    </row>
+    <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C310" s="4"/>
+      <c r="O310" s="4"/>
+    </row>
+    <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C311" s="4"/>
+      <c r="O311" s="4"/>
+    </row>
+    <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C312" s="4"/>
+      <c r="O312" s="4"/>
+    </row>
+    <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C313" s="4"/>
+      <c r="O313" s="4"/>
+    </row>
+    <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C314" s="4"/>
+      <c r="O314" s="4"/>
+    </row>
+    <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C315" s="4"/>
+      <c r="O315" s="4"/>
+    </row>
+    <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C316" s="4"/>
+      <c r="O316" s="4"/>
+    </row>
+    <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C317" s="4"/>
+      <c r="O317" s="4"/>
+    </row>
+    <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C318" s="4"/>
+      <c r="O318" s="4"/>
+    </row>
+    <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C319" s="4"/>
+      <c r="O319" s="4"/>
+    </row>
+    <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C320" s="4"/>
+      <c r="O320" s="4"/>
+    </row>
+    <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C321" s="4"/>
+      <c r="O321" s="4"/>
+    </row>
+    <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C322" s="4"/>
+      <c r="O322" s="4"/>
+    </row>
+    <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C323" s="4"/>
+      <c r="O323" s="4"/>
+    </row>
+    <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C324" s="4"/>
+      <c r="O324" s="4"/>
+    </row>
+    <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C325" s="4"/>
+      <c r="O325" s="4"/>
+    </row>
+    <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C326" s="4"/>
+      <c r="O326" s="4"/>
+    </row>
+    <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C327" s="4"/>
+      <c r="O327" s="4"/>
+    </row>
+    <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C328" s="4"/>
+      <c r="O328" s="4"/>
+    </row>
+    <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C329" s="4"/>
+      <c r="O329" s="4"/>
+    </row>
+    <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C330" s="4"/>
+      <c r="O330" s="4"/>
+    </row>
+    <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C331" s="4"/>
+      <c r="O331" s="4"/>
+    </row>
+    <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C332" s="4"/>
+      <c r="O332" s="4"/>
+    </row>
+    <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C333" s="4"/>
+      <c r="O333" s="4"/>
+    </row>
+    <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C334" s="4"/>
+      <c r="O334" s="4"/>
+    </row>
+    <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C335" s="4"/>
+      <c r="O335" s="4"/>
+    </row>
+    <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C336" s="4"/>
+      <c r="O336" s="4"/>
+    </row>
+    <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C337" s="4"/>
+      <c r="O337" s="4"/>
+    </row>
+    <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C338" s="4"/>
+      <c r="O338" s="4"/>
+    </row>
+    <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C339" s="4"/>
+      <c r="O339" s="4"/>
+    </row>
+    <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C340" s="4"/>
+      <c r="O340" s="4"/>
+    </row>
+    <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C341" s="4"/>
+      <c r="O341" s="4"/>
+    </row>
+    <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C342" s="4"/>
+      <c r="O342" s="4"/>
+    </row>
+    <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C343" s="4"/>
+      <c r="O343" s="4"/>
+    </row>
+    <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C344" s="4"/>
+      <c r="O344" s="4"/>
+    </row>
+    <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C345" s="4"/>
+      <c r="O345" s="4"/>
+    </row>
+    <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C346" s="4"/>
+      <c r="O346" s="4"/>
+    </row>
+    <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C347" s="4"/>
+      <c r="O347" s="4"/>
+    </row>
+    <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C348" s="4"/>
+      <c r="O348" s="4"/>
+    </row>
+    <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C349" s="4"/>
+      <c r="O349" s="4"/>
+    </row>
+    <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C350" s="4"/>
+      <c r="O350" s="4"/>
+    </row>
+    <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C351" s="4"/>
+      <c r="O351" s="4"/>
+    </row>
+    <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C352" s="4"/>
+      <c r="O352" s="4"/>
+    </row>
+    <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C353" s="4"/>
+      <c r="O353" s="4"/>
+    </row>
+    <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C354" s="4"/>
+      <c r="O354" s="4"/>
+    </row>
+    <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C355" s="4"/>
+      <c r="O355" s="4"/>
+    </row>
+    <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C356" s="4"/>
+      <c r="O356" s="4"/>
+    </row>
+    <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C357" s="4"/>
+      <c r="O357" s="4"/>
+    </row>
+    <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C358" s="4"/>
+      <c r="O358" s="4"/>
+    </row>
+    <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C359" s="4"/>
+      <c r="O359" s="4"/>
+    </row>
+    <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C360" s="4"/>
+      <c r="O360" s="4"/>
+    </row>
+    <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C361" s="4"/>
+      <c r="O361" s="4"/>
+    </row>
+    <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C362" s="4"/>
+      <c r="O362" s="4"/>
+    </row>
+    <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C363" s="4"/>
+      <c r="O363" s="4"/>
+    </row>
+    <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C364" s="4"/>
+      <c r="O364" s="4"/>
+    </row>
+    <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C365" s="4"/>
+      <c r="O365" s="4"/>
+    </row>
+    <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C366" s="4"/>
+      <c r="O366" s="4"/>
+    </row>
+    <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C367" s="4"/>
+      <c r="O367" s="4"/>
+    </row>
+    <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C368" s="4"/>
+      <c r="O368" s="4"/>
+    </row>
+    <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C369" s="4"/>
+      <c r="O369" s="4"/>
+    </row>
+    <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C370" s="4"/>
+      <c r="O370" s="4"/>
+    </row>
+    <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C371" s="4"/>
+      <c r="O371" s="4"/>
+    </row>
+    <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C372" s="4"/>
+      <c r="O372" s="4"/>
+    </row>
+    <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C373" s="4"/>
+      <c r="O373" s="4"/>
+    </row>
+    <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C374" s="4"/>
+      <c r="O374" s="4"/>
+    </row>
+    <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C375" s="4"/>
+      <c r="O375" s="4"/>
+    </row>
+    <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C376" s="4"/>
+      <c r="O376" s="4"/>
+    </row>
+    <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C377" s="4"/>
+      <c r="O377" s="4"/>
+    </row>
+    <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C378" s="4"/>
+      <c r="O378" s="4"/>
+    </row>
+    <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C379" s="4"/>
+      <c r="O379" s="4"/>
+    </row>
+    <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C380" s="4"/>
+      <c r="O380" s="4"/>
+    </row>
+    <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C381" s="4"/>
+      <c r="O381" s="4"/>
+    </row>
+    <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C382" s="4"/>
+      <c r="O382" s="4"/>
+    </row>
+    <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C383" s="4"/>
+      <c r="O383" s="4"/>
+    </row>
+    <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C384" s="4"/>
+      <c r="O384" s="4"/>
+    </row>
+    <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C385" s="4"/>
+      <c r="O385" s="4"/>
+    </row>
+    <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C386" s="4"/>
+      <c r="O386" s="4"/>
+    </row>
+    <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C387" s="4"/>
+      <c r="O387" s="4"/>
+    </row>
+    <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C388" s="4"/>
+      <c r="O388" s="4"/>
+    </row>
+    <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C389" s="4"/>
+      <c r="O389" s="4"/>
+    </row>
+    <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C390" s="4"/>
+      <c r="O390" s="4"/>
+    </row>
+    <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C391" s="4"/>
+      <c r="O391" s="4"/>
+    </row>
+    <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C392" s="4"/>
+      <c r="O392" s="4"/>
+    </row>
+    <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C393" s="4"/>
+      <c r="O393" s="4"/>
+    </row>
+    <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C394" s="4"/>
+      <c r="O394" s="4"/>
+    </row>
+    <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C395" s="4"/>
+      <c r="O395" s="4"/>
+    </row>
+    <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C396" s="4"/>
+      <c r="O396" s="4"/>
+    </row>
+    <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C397" s="4"/>
+      <c r="O397" s="4"/>
+    </row>
+    <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C398" s="4"/>
+      <c r="O398" s="4"/>
+    </row>
+    <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C399" s="4"/>
+      <c r="O399" s="4"/>
+    </row>
+    <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C400" s="4"/>
+      <c r="O400" s="4"/>
+    </row>
+    <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C401" s="4"/>
+      <c r="O401" s="4"/>
+    </row>
+    <row r="402" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C402" s="4"/>
+      <c r="O402" s="4"/>
+    </row>
+    <row r="403" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C403" s="4"/>
+      <c r="O403" s="4"/>
+    </row>
+    <row r="404" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C404" s="4"/>
+      <c r="O404" s="4"/>
+    </row>
+    <row r="405" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C405" s="4"/>
+      <c r="O405" s="4"/>
+    </row>
+    <row r="406" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C406" s="4"/>
+      <c r="O406" s="4"/>
+    </row>
+    <row r="407" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C407" s="4"/>
+      <c r="O407" s="4"/>
+    </row>
+    <row r="408" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C408" s="4"/>
+      <c r="O408" s="4"/>
+    </row>
+    <row r="409" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C409" s="4"/>
+      <c r="O409" s="4"/>
+    </row>
+    <row r="410" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C410" s="4"/>
+      <c r="O410" s="4"/>
+    </row>
+    <row r="411" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C411" s="4"/>
+      <c r="O411" s="4"/>
+    </row>
+    <row r="412" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C412" s="4"/>
+      <c r="O412" s="4"/>
+    </row>
+    <row r="413" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C413" s="4"/>
+      <c r="O413" s="4"/>
+    </row>
+    <row r="414" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C414" s="4"/>
+      <c r="O414" s="4"/>
+    </row>
+    <row r="415" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C415" s="4"/>
+      <c r="O415" s="4"/>
+    </row>
+    <row r="416" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C416" s="4"/>
+      <c r="O416" s="4"/>
+    </row>
+    <row r="417" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C417" s="4"/>
+      <c r="O417" s="4"/>
+    </row>
+    <row r="418" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C418" s="4"/>
+      <c r="O418" s="4"/>
+    </row>
+    <row r="419" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C419" s="4"/>
+      <c r="O419" s="4"/>
+    </row>
+    <row r="420" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C420" s="4"/>
+      <c r="O420" s="4"/>
+    </row>
+    <row r="421" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C421" s="4"/>
+      <c r="O421" s="4"/>
+    </row>
+    <row r="422" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C422" s="4"/>
+      <c r="O422" s="4"/>
+    </row>
+    <row r="423" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C423" s="4"/>
+      <c r="O423" s="4"/>
+    </row>
+    <row r="424" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C424" s="4"/>
+      <c r="O424" s="4"/>
+    </row>
+    <row r="425" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C425" s="4"/>
+      <c r="O425" s="4"/>
+    </row>
+    <row r="426" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C426" s="4"/>
+      <c r="O426" s="4"/>
+    </row>
+    <row r="427" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C427" s="4"/>
+      <c r="O427" s="4"/>
+    </row>
+    <row r="428" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C428" s="4"/>
+      <c r="O428" s="4"/>
+    </row>
+    <row r="429" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C429" s="4"/>
+      <c r="O429" s="4"/>
+    </row>
+    <row r="430" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C430" s="4"/>
+      <c r="O430" s="4"/>
+    </row>
+    <row r="431" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C431" s="4"/>
+      <c r="O431" s="4"/>
+    </row>
+    <row r="432" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C432" s="4"/>
+      <c r="O432" s="4"/>
+    </row>
+    <row r="433" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C433" s="4"/>
+      <c r="O433" s="4"/>
+    </row>
+    <row r="434" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C434" s="4"/>
+      <c r="O434" s="4"/>
+    </row>
+    <row r="435" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C435" s="4"/>
+      <c r="O435" s="4"/>
+    </row>
+    <row r="436" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C436" s="4"/>
+      <c r="O436" s="4"/>
+    </row>
+    <row r="437" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C437" s="4"/>
+      <c r="O437" s="4"/>
+    </row>
+    <row r="438" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C438" s="4"/>
+      <c r="O438" s="4"/>
+    </row>
+    <row r="439" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C439" s="4"/>
+      <c r="O439" s="4"/>
+    </row>
+    <row r="440" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C440" s="4"/>
+      <c r="O440" s="4"/>
+    </row>
+    <row r="441" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C441" s="4"/>
+      <c r="O441" s="4"/>
+    </row>
+    <row r="442" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C442" s="4"/>
+      <c r="O442" s="4"/>
+    </row>
+    <row r="443" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C443" s="4"/>
+      <c r="O443" s="4"/>
+    </row>
+    <row r="444" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C444" s="4"/>
+      <c r="O444" s="4"/>
+    </row>
+    <row r="445" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C445" s="4"/>
+      <c r="O445" s="4"/>
+    </row>
+    <row r="446" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C446" s="4"/>
+      <c r="O446" s="4"/>
+    </row>
+    <row r="447" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C447" s="4"/>
+      <c r="O447" s="4"/>
+    </row>
+    <row r="448" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C448" s="4"/>
+      <c r="O448" s="4"/>
+    </row>
+    <row r="449" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C449" s="4"/>
+      <c r="O449" s="4"/>
+    </row>
+    <row r="450" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C450" s="4"/>
+      <c r="O450" s="4"/>
+    </row>
+    <row r="451" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C451" s="4"/>
+      <c r="O451" s="4"/>
+    </row>
+    <row r="452" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C452" s="4"/>
+      <c r="O452" s="4"/>
+    </row>
+    <row r="453" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C453" s="4"/>
+      <c r="O453" s="4"/>
+    </row>
+    <row r="454" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C454" s="4"/>
+      <c r="O454" s="4"/>
+    </row>
+    <row r="455" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C455" s="4"/>
+      <c r="O455" s="4"/>
+    </row>
+    <row r="456" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C456" s="4"/>
+      <c r="O456" s="4"/>
+    </row>
+    <row r="457" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C457" s="4"/>
+      <c r="O457" s="4"/>
+    </row>
+    <row r="458" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C458" s="4"/>
+      <c r="O458" s="4"/>
+    </row>
+    <row r="459" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C459" s="4"/>
+      <c r="O459" s="4"/>
+    </row>
+    <row r="460" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C460" s="4"/>
+      <c r="O460" s="4"/>
+    </row>
+    <row r="461" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C461" s="4"/>
+      <c r="O461" s="4"/>
+    </row>
+    <row r="462" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C462" s="4"/>
+      <c r="O462" s="4"/>
+    </row>
+    <row r="463" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C463" s="4"/>
+      <c r="O463" s="4"/>
+    </row>
+    <row r="464" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C464" s="4"/>
+      <c r="O464" s="4"/>
+    </row>
+    <row r="465" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C465" s="4"/>
+      <c r="O465" s="4"/>
+    </row>
+    <row r="466" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C466" s="4"/>
+      <c r="O466" s="4"/>
+    </row>
+    <row r="467" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C467" s="4"/>
+      <c r="O467" s="4"/>
+    </row>
+    <row r="468" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C468" s="4"/>
+      <c r="O468" s="4"/>
+    </row>
+    <row r="469" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C469" s="4"/>
+      <c r="O469" s="4"/>
+    </row>
+    <row r="470" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C470" s="4"/>
+      <c r="O470" s="4"/>
+    </row>
+    <row r="471" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C471" s="4"/>
+      <c r="O471" s="4"/>
+    </row>
+    <row r="472" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C472" s="4"/>
+      <c r="O472" s="4"/>
+    </row>
+    <row r="473" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C473" s="4"/>
+      <c r="O473" s="4"/>
+    </row>
+    <row r="474" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C474" s="4"/>
+      <c r="O474" s="4"/>
+    </row>
+    <row r="475" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C475" s="4"/>
+      <c r="O475" s="4"/>
+    </row>
+    <row r="476" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C476" s="4"/>
+      <c r="O476" s="4"/>
+    </row>
+    <row r="477" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C477" s="4"/>
+      <c r="O477" s="4"/>
+    </row>
+    <row r="478" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C478" s="4"/>
+      <c r="O478" s="4"/>
+    </row>
+    <row r="479" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C479" s="4"/>
+      <c r="O479" s="4"/>
+    </row>
+    <row r="480" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C480" s="4"/>
+      <c r="O480" s="4"/>
+    </row>
+    <row r="481" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C481" s="4"/>
+      <c r="O481" s="4"/>
+    </row>
+    <row r="482" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C482" s="4"/>
+      <c r="O482" s="4"/>
+    </row>
+    <row r="483" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C483" s="4"/>
+      <c r="O483" s="4"/>
+    </row>
+    <row r="484" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C484" s="4"/>
+      <c r="O484" s="4"/>
+    </row>
+    <row r="485" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C485" s="4"/>
+      <c r="O485" s="4"/>
+    </row>
+    <row r="486" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C486" s="4"/>
+      <c r="O486" s="4"/>
+    </row>
+    <row r="487" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C487" s="4"/>
+      <c r="O487" s="4"/>
+    </row>
+    <row r="488" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C488" s="4"/>
+      <c r="O488" s="4"/>
+    </row>
+    <row r="489" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C489" s="4"/>
+      <c r="O489" s="4"/>
+    </row>
+    <row r="490" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C490" s="4"/>
+      <c r="O490" s="4"/>
+    </row>
+    <row r="491" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C491" s="4"/>
+      <c r="O491" s="4"/>
+    </row>
+    <row r="492" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C492" s="4"/>
+      <c r="O492" s="4"/>
+    </row>
+    <row r="493" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C493" s="4"/>
+      <c r="O493" s="4"/>
+    </row>
+    <row r="494" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C494" s="4"/>
+      <c r="O494" s="4"/>
+    </row>
+    <row r="495" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C495" s="4"/>
+      <c r="O495" s="4"/>
+    </row>
+    <row r="496" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C496" s="4"/>
+      <c r="O496" s="4"/>
+    </row>
+    <row r="497" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C497" s="4"/>
+      <c r="O497" s="4"/>
+    </row>
+    <row r="498" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C498" s="4"/>
+      <c r="O498" s="4"/>
+    </row>
+    <row r="499" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C499" s="4"/>
+      <c r="O499" s="4"/>
+    </row>
+    <row r="500" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C500" s="4"/>
+      <c r="O500" s="4"/>
+    </row>
+    <row r="501" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C501" s="4"/>
+      <c r="O501" s="4"/>
+    </row>
+    <row r="502" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C502" s="4"/>
+      <c r="O502" s="4"/>
+    </row>
+    <row r="503" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C503" s="4"/>
+      <c r="O503" s="4"/>
+    </row>
+    <row r="504" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C504" s="4"/>
+      <c r="O504" s="4"/>
+    </row>
+    <row r="505" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C505" s="4"/>
+      <c r="O505" s="4"/>
+    </row>
+    <row r="506" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C506" s="4"/>
+      <c r="O506" s="4"/>
+    </row>
+    <row r="507" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C507" s="4"/>
+      <c r="O507" s="4"/>
+    </row>
+    <row r="508" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C508" s="4"/>
+      <c r="O508" s="4"/>
+    </row>
+    <row r="509" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C509" s="4"/>
+      <c r="O509" s="4"/>
+    </row>
+    <row r="510" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C510" s="4"/>
+      <c r="O510" s="4"/>
+    </row>
+    <row r="511" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C511" s="4"/>
+      <c r="O511" s="4"/>
+    </row>
+    <row r="512" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C512" s="4"/>
+      <c r="O512" s="4"/>
+    </row>
+    <row r="513" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C513" s="4"/>
+      <c r="O513" s="4"/>
+    </row>
+    <row r="514" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C514" s="4"/>
+      <c r="O514" s="4"/>
+    </row>
+    <row r="515" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C515" s="4"/>
+      <c r="O515" s="4"/>
+    </row>
+    <row r="516" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C516" s="4"/>
+      <c r="O516" s="4"/>
+    </row>
+    <row r="517" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C517" s="4"/>
+      <c r="O517" s="4"/>
+    </row>
+    <row r="518" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C518" s="4"/>
+      <c r="O518" s="4"/>
+    </row>
+    <row r="519" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C519" s="4"/>
+      <c r="O519" s="4"/>
+    </row>
+    <row r="520" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C520" s="4"/>
+      <c r="O520" s="4"/>
+    </row>
+    <row r="521" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C521" s="4"/>
+      <c r="O521" s="4"/>
+    </row>
+    <row r="522" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C522" s="4"/>
+      <c r="O522" s="4"/>
+    </row>
+    <row r="523" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C523" s="4"/>
+      <c r="O523" s="4"/>
+    </row>
+    <row r="524" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C524" s="4"/>
+      <c r="O524" s="4"/>
+    </row>
+    <row r="525" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C525" s="4"/>
+      <c r="O525" s="4"/>
+    </row>
+    <row r="526" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C526" s="4"/>
+      <c r="O526" s="4"/>
+    </row>
+    <row r="527" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C527" s="4"/>
+      <c r="O527" s="4"/>
+    </row>
+    <row r="528" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C528" s="4"/>
+      <c r="O528" s="4"/>
+    </row>
+    <row r="529" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C529" s="4"/>
+      <c r="O529" s="4"/>
+    </row>
+    <row r="530" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C530" s="4"/>
+      <c r="O530" s="4"/>
+    </row>
+    <row r="531" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C531" s="4"/>
+      <c r="O531" s="4"/>
+    </row>
+    <row r="532" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C532" s="4"/>
+      <c r="O532" s="4"/>
+    </row>
+    <row r="533" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C533" s="4"/>
+      <c r="O533" s="4"/>
+    </row>
+    <row r="534" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C534" s="4"/>
+      <c r="O534" s="4"/>
+    </row>
+    <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C535" s="4"/>
+      <c r="O535" s="4"/>
+    </row>
+    <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C536" s="4"/>
+      <c r="O536" s="4"/>
+    </row>
+    <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C537" s="4"/>
+      <c r="O537" s="4"/>
+    </row>
+    <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C538" s="4"/>
+      <c r="O538" s="4"/>
+    </row>
+    <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C539" s="4"/>
+      <c r="O539" s="4"/>
+    </row>
+    <row r="540" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C540" s="4"/>
+      <c r="O540" s="4"/>
+    </row>
+    <row r="541" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C541" s="4"/>
+      <c r="O541" s="4"/>
+    </row>
+    <row r="542" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C542" s="4"/>
+      <c r="O542" s="4"/>
+    </row>
+    <row r="543" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C543" s="4"/>
+      <c r="O543" s="4"/>
+    </row>
+    <row r="544" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C544" s="4"/>
+      <c r="O544" s="4"/>
+    </row>
+    <row r="545" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C545" s="4"/>
+      <c r="O545" s="4"/>
+    </row>
+    <row r="546" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C546" s="4"/>
+      <c r="O546" s="4"/>
+    </row>
+    <row r="547" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C547" s="4"/>
+      <c r="O547" s="4"/>
+    </row>
+    <row r="548" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C548" s="4"/>
+      <c r="O548" s="4"/>
+    </row>
+    <row r="549" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C549" s="4"/>
+      <c r="O549" s="4"/>
+    </row>
+    <row r="550" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C550" s="4"/>
+      <c r="O550" s="4"/>
+    </row>
+    <row r="551" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C551" s="4"/>
+      <c r="O551" s="4"/>
+    </row>
+    <row r="552" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C552" s="4"/>
+      <c r="O552" s="4"/>
+    </row>
+    <row r="553" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C553" s="4"/>
+      <c r="O553" s="4"/>
+    </row>
+    <row r="554" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C554" s="4"/>
+      <c r="O554" s="4"/>
+    </row>
+    <row r="555" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C555" s="4"/>
+      <c r="O555" s="4"/>
+    </row>
+    <row r="556" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C556" s="4"/>
+      <c r="O556" s="4"/>
+    </row>
+    <row r="557" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C557" s="4"/>
+      <c r="O557" s="4"/>
+    </row>
+    <row r="558" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C558" s="4"/>
+      <c r="O558" s="4"/>
+    </row>
+    <row r="559" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C559" s="4"/>
+      <c r="O559" s="4"/>
+    </row>
+    <row r="560" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C560" s="4"/>
+      <c r="O560" s="4"/>
+    </row>
+    <row r="561" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C561" s="4"/>
+      <c r="O561" s="4"/>
+    </row>
+    <row r="562" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C562" s="4"/>
+      <c r="O562" s="4"/>
+    </row>
+    <row r="563" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C563" s="4"/>
+      <c r="O563" s="4"/>
+    </row>
+    <row r="564" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C564" s="4"/>
+      <c r="O564" s="4"/>
+    </row>
+    <row r="565" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C565" s="4"/>
+      <c r="O565" s="4"/>
+    </row>
+    <row r="566" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C566" s="4"/>
+      <c r="O566" s="4"/>
+    </row>
+    <row r="567" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C567" s="4"/>
+      <c r="O567" s="4"/>
+    </row>
+    <row r="568" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C568" s="4"/>
+      <c r="O568" s="4"/>
+    </row>
+    <row r="569" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C569" s="4"/>
+      <c r="O569" s="4"/>
+    </row>
+    <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C570" s="4"/>
+      <c r="O570" s="4"/>
+    </row>
+    <row r="571" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C571" s="4"/>
+      <c r="O571" s="4"/>
+    </row>
+    <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C572" s="4"/>
+      <c r="O572" s="4"/>
+    </row>
+    <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C573" s="4"/>
+      <c r="O573" s="4"/>
+    </row>
+    <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C574" s="4"/>
+      <c r="O574" s="4"/>
+    </row>
+    <row r="575" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C575" s="4"/>
+      <c r="O575" s="4"/>
+    </row>
+    <row r="576" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C576" s="4"/>
+      <c r="O576" s="4"/>
+    </row>
+    <row r="577" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C577" s="4"/>
+      <c r="O577" s="4"/>
+    </row>
+    <row r="578" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C578" s="4"/>
+      <c r="O578" s="4"/>
+    </row>
+    <row r="579" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C579" s="4"/>
+      <c r="O579" s="4"/>
+    </row>
+    <row r="580" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C580" s="4"/>
+      <c r="O580" s="4"/>
+    </row>
+    <row r="581" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C581" s="4"/>
+      <c r="O581" s="4"/>
+    </row>
+    <row r="582" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C582" s="4"/>
+      <c r="O582" s="4"/>
+    </row>
+    <row r="583" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C583" s="4"/>
+      <c r="O583" s="4"/>
+    </row>
+    <row r="584" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C584" s="4"/>
+      <c r="O584" s="4"/>
+    </row>
+    <row r="585" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C585" s="4"/>
+      <c r="O585" s="4"/>
+    </row>
+    <row r="586" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C586" s="4"/>
+      <c r="O586" s="4"/>
+    </row>
+    <row r="587" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C587" s="4"/>
+      <c r="O587" s="4"/>
+    </row>
+    <row r="588" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C588" s="4"/>
+      <c r="O588" s="4"/>
+    </row>
+    <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C589" s="4"/>
+      <c r="O589" s="4"/>
+    </row>
+    <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C590" s="4"/>
+      <c r="O590" s="4"/>
+    </row>
+    <row r="591" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C591" s="4"/>
+      <c r="O591" s="4"/>
+    </row>
+    <row r="592" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C592" s="4"/>
+      <c r="O592" s="4"/>
+    </row>
+    <row r="593" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C593" s="4"/>
+      <c r="O593" s="4"/>
+    </row>
+    <row r="594" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C594" s="4"/>
+      <c r="O594" s="4"/>
+    </row>
+    <row r="595" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C595" s="4"/>
+      <c r="O595" s="4"/>
+    </row>
+    <row r="596" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C596" s="4"/>
+      <c r="O596" s="4"/>
+    </row>
+    <row r="597" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C597" s="4"/>
+      <c r="O597" s="4"/>
+    </row>
+    <row r="598" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C598" s="4"/>
+      <c r="O598" s="4"/>
+    </row>
+    <row r="599" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C599" s="4"/>
+      <c r="O599" s="4"/>
+    </row>
+    <row r="600" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C600" s="4"/>
+      <c r="O600" s="4"/>
+    </row>
+    <row r="601" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C601" s="4"/>
+      <c r="O601" s="4"/>
+    </row>
+    <row r="602" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C602" s="4"/>
+      <c r="O602" s="4"/>
+    </row>
+    <row r="603" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C603" s="4"/>
+      <c r="O603" s="4"/>
+    </row>
+    <row r="604" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C604" s="4"/>
+      <c r="O604" s="4"/>
+    </row>
+    <row r="605" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C605" s="4"/>
+      <c r="O605" s="4"/>
+    </row>
+    <row r="606" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C606" s="4"/>
+      <c r="O606" s="4"/>
+    </row>
+    <row r="607" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C607" s="4"/>
+      <c r="O607" s="4"/>
+    </row>
+    <row r="608" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C608" s="4"/>
+      <c r="O608" s="4"/>
+    </row>
+    <row r="609" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C609" s="4"/>
+      <c r="O609" s="4"/>
+    </row>
+    <row r="610" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C610" s="4"/>
+      <c r="O610" s="4"/>
+    </row>
+    <row r="611" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C611" s="4"/>
+      <c r="O611" s="4"/>
+    </row>
+    <row r="612" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C612" s="4"/>
+      <c r="O612" s="4"/>
+    </row>
+    <row r="613" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C613" s="4"/>
+      <c r="O613" s="4"/>
+    </row>
+    <row r="614" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C614" s="4"/>
+      <c r="O614" s="4"/>
+    </row>
+    <row r="615" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C615" s="4"/>
+      <c r="O615" s="4"/>
+    </row>
+    <row r="616" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C616" s="4"/>
+      <c r="O616" s="4"/>
+    </row>
+    <row r="617" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C617" s="4"/>
+      <c r="O617" s="4"/>
+    </row>
+    <row r="618" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C618" s="4"/>
+      <c r="O618" s="4"/>
+    </row>
+    <row r="619" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C619" s="4"/>
+      <c r="O619" s="4"/>
+    </row>
+    <row r="620" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C620" s="4"/>
+      <c r="O620" s="4"/>
+    </row>
+    <row r="621" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C621" s="4"/>
+      <c r="O621" s="4"/>
+    </row>
+    <row r="622" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C622" s="4"/>
+      <c r="O622" s="4"/>
+    </row>
+    <row r="623" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C623" s="4"/>
+      <c r="O623" s="4"/>
+    </row>
+    <row r="624" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C624" s="4"/>
+      <c r="O624" s="4"/>
+    </row>
+    <row r="625" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C625" s="4"/>
+      <c r="O625" s="4"/>
+    </row>
+    <row r="626" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C626" s="4"/>
+      <c r="O626" s="4"/>
+    </row>
+    <row r="627" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C627" s="4"/>
+      <c r="O627" s="4"/>
+    </row>
+    <row r="628" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C628" s="4"/>
+      <c r="O628" s="4"/>
+    </row>
+    <row r="629" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C629" s="4"/>
+      <c r="O629" s="4"/>
+    </row>
+    <row r="630" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C630" s="4"/>
+      <c r="O630" s="4"/>
+    </row>
+    <row r="631" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C631" s="4"/>
+      <c r="O631" s="4"/>
+    </row>
+    <row r="632" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C632" s="4"/>
+      <c r="O632" s="4"/>
+    </row>
+    <row r="633" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C633" s="4"/>
+      <c r="O633" s="4"/>
+    </row>
+    <row r="634" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C634" s="4"/>
+      <c r="O634" s="4"/>
+    </row>
+    <row r="635" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C635" s="4"/>
+      <c r="O635" s="4"/>
+    </row>
+    <row r="636" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C636" s="4"/>
+      <c r="O636" s="4"/>
+    </row>
+    <row r="637" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C637" s="4"/>
+      <c r="O637" s="4"/>
+    </row>
+    <row r="638" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C638" s="4"/>
+      <c r="O638" s="4"/>
+    </row>
+    <row r="639" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C639" s="4"/>
+      <c r="O639" s="4"/>
+    </row>
+    <row r="640" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C640" s="4"/>
+      <c r="O640" s="4"/>
+    </row>
+    <row r="641" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C641" s="4"/>
+      <c r="O641" s="4"/>
+    </row>
+    <row r="642" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C642" s="4"/>
+      <c r="O642" s="4"/>
+    </row>
+    <row r="643" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C643" s="4"/>
+      <c r="O643" s="4"/>
+    </row>
+    <row r="644" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C644" s="4"/>
+      <c r="O644" s="4"/>
+    </row>
+    <row r="645" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C645" s="4"/>
+      <c r="O645" s="4"/>
+    </row>
+    <row r="646" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C646" s="4"/>
+      <c r="O646" s="4"/>
+    </row>
+    <row r="647" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C647" s="4"/>
+      <c r="O647" s="4"/>
+    </row>
+    <row r="648" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C648" s="4"/>
+      <c r="O648" s="4"/>
+    </row>
+    <row r="649" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C649" s="4"/>
+      <c r="O649" s="4"/>
+    </row>
+    <row r="650" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C650" s="4"/>
+      <c r="O650" s="4"/>
+    </row>
+    <row r="651" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C651" s="4"/>
+      <c r="O651" s="4"/>
+    </row>
+    <row r="652" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C652" s="4"/>
+      <c r="O652" s="4"/>
+    </row>
+    <row r="653" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C653" s="4"/>
+      <c r="O653" s="4"/>
+    </row>
+    <row r="654" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C654" s="4"/>
+      <c r="O654" s="4"/>
+    </row>
+    <row r="655" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C655" s="4"/>
+      <c r="O655" s="4"/>
+    </row>
+    <row r="656" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C656" s="4"/>
+      <c r="O656" s="4"/>
+    </row>
+    <row r="657" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C657" s="4"/>
+      <c r="O657" s="4"/>
+    </row>
+    <row r="658" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C658" s="4"/>
+      <c r="O658" s="4"/>
+    </row>
+    <row r="659" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C659" s="4"/>
+      <c r="O659" s="4"/>
+    </row>
+    <row r="660" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C660" s="4"/>
+      <c r="O660" s="4"/>
+    </row>
+    <row r="661" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C661" s="4"/>
+      <c r="O661" s="4"/>
+    </row>
+    <row r="662" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C662" s="4"/>
+      <c r="O662" s="4"/>
+    </row>
+    <row r="663" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C663" s="4"/>
+      <c r="O663" s="4"/>
+    </row>
+    <row r="664" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C664" s="4"/>
+      <c r="O664" s="4"/>
+    </row>
+    <row r="665" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C665" s="4"/>
+      <c r="O665" s="4"/>
+    </row>
+    <row r="666" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C666" s="4"/>
+      <c r="O666" s="4"/>
+    </row>
+    <row r="667" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C667" s="4"/>
+      <c r="O667" s="4"/>
+    </row>
+    <row r="668" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C668" s="4"/>
+      <c r="O668" s="4"/>
+    </row>
+    <row r="669" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C669" s="4"/>
+      <c r="O669" s="4"/>
+    </row>
+    <row r="670" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C670" s="4"/>
+      <c r="O670" s="4"/>
+    </row>
+    <row r="671" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C671" s="4"/>
+      <c r="O671" s="4"/>
+    </row>
+    <row r="672" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C672" s="4"/>
+      <c r="O672" s="4"/>
+    </row>
+    <row r="673" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C673" s="4"/>
+      <c r="O673" s="4"/>
+    </row>
+    <row r="674" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C674" s="4"/>
+      <c r="O674" s="4"/>
+    </row>
+    <row r="675" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C675" s="4"/>
+      <c r="O675" s="4"/>
+    </row>
+    <row r="676" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C676" s="4"/>
+      <c r="O676" s="4"/>
+    </row>
+    <row r="677" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C677" s="4"/>
+      <c r="O677" s="4"/>
+    </row>
+    <row r="678" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C678" s="4"/>
+      <c r="O678" s="4"/>
+    </row>
+    <row r="679" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C679" s="4"/>
+      <c r="O679" s="4"/>
+    </row>
+    <row r="680" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C680" s="4"/>
+      <c r="O680" s="4"/>
+    </row>
+    <row r="681" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C681" s="4"/>
+      <c r="O681" s="4"/>
+    </row>
+    <row r="682" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C682" s="4"/>
+      <c r="O682" s="4"/>
+    </row>
+    <row r="683" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C683" s="4"/>
+      <c r="O683" s="4"/>
+    </row>
+    <row r="684" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C684" s="4"/>
+      <c r="O684" s="4"/>
+    </row>
+    <row r="685" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C685" s="4"/>
+      <c r="O685" s="4"/>
+    </row>
+    <row r="686" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C686" s="4"/>
+      <c r="O686" s="4"/>
+    </row>
+    <row r="687" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C687" s="4"/>
+      <c r="O687" s="4"/>
+    </row>
+    <row r="688" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C688" s="4"/>
+      <c r="O688" s="4"/>
+    </row>
+    <row r="689" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C689" s="4"/>
+      <c r="O689" s="4"/>
+    </row>
+    <row r="690" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C690" s="4"/>
+      <c r="O690" s="4"/>
+    </row>
+    <row r="691" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C691" s="4"/>
+      <c r="O691" s="4"/>
+    </row>
+    <row r="692" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C692" s="4"/>
+      <c r="O692" s="4"/>
+    </row>
+    <row r="693" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C693" s="4"/>
+      <c r="O693" s="4"/>
+    </row>
+    <row r="694" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C694" s="4"/>
+      <c r="O694" s="4"/>
+    </row>
+    <row r="695" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C695" s="4"/>
+      <c r="O695" s="4"/>
+    </row>
+    <row r="696" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C696" s="4"/>
+      <c r="O696" s="4"/>
+    </row>
+    <row r="697" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C697" s="4"/>
+      <c r="O697" s="4"/>
+    </row>
+    <row r="698" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C698" s="4"/>
+      <c r="O698" s="4"/>
+    </row>
+    <row r="699" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C699" s="4"/>
+      <c r="O699" s="4"/>
+    </row>
+    <row r="700" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C700" s="4"/>
+      <c r="O700" s="4"/>
+    </row>
+    <row r="701" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C701" s="4"/>
+      <c r="O701" s="4"/>
+    </row>
+    <row r="702" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C702" s="4"/>
+      <c r="O702" s="4"/>
+    </row>
+    <row r="703" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C703" s="4"/>
+      <c r="O703" s="4"/>
+    </row>
+    <row r="704" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C704" s="4"/>
+      <c r="O704" s="4"/>
+    </row>
+    <row r="705" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C705" s="4"/>
+      <c r="O705" s="4"/>
+    </row>
+    <row r="706" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C706" s="4"/>
+      <c r="O706" s="4"/>
+    </row>
+    <row r="707" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C707" s="4"/>
+      <c r="O707" s="4"/>
+    </row>
+    <row r="708" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C708" s="4"/>
+      <c r="O708" s="4"/>
+    </row>
+    <row r="709" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C709" s="4"/>
+      <c r="O709" s="4"/>
+    </row>
+    <row r="710" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C710" s="4"/>
+      <c r="O710" s="4"/>
+    </row>
+    <row r="711" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C711" s="4"/>
+      <c r="O711" s="4"/>
+    </row>
+    <row r="712" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C712" s="4"/>
+      <c r="O712" s="4"/>
+    </row>
+    <row r="713" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C713" s="4"/>
+      <c r="O713" s="4"/>
+    </row>
+    <row r="714" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C714" s="4"/>
+      <c r="O714" s="4"/>
+    </row>
+    <row r="715" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C715" s="4"/>
+      <c r="O715" s="4"/>
+    </row>
+    <row r="716" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C716" s="4"/>
+      <c r="O716" s="4"/>
+    </row>
+    <row r="717" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C717" s="4"/>
+      <c r="O717" s="4"/>
+    </row>
+    <row r="718" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C718" s="4"/>
+      <c r="O718" s="4"/>
+    </row>
+    <row r="719" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C719" s="4"/>
+      <c r="O719" s="4"/>
+    </row>
+    <row r="720" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C720" s="4"/>
+      <c r="O720" s="4"/>
+    </row>
+    <row r="721" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C721" s="4"/>
+      <c r="O721" s="4"/>
+    </row>
+    <row r="722" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C722" s="4"/>
+      <c r="O722" s="4"/>
+    </row>
+    <row r="723" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C723" s="4"/>
+      <c r="O723" s="4"/>
+    </row>
+    <row r="724" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C724" s="4"/>
+      <c r="O724" s="4"/>
+    </row>
+    <row r="725" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C725" s="4"/>
+      <c r="O725" s="4"/>
+    </row>
+    <row r="726" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C726" s="4"/>
+      <c r="O726" s="4"/>
+    </row>
+    <row r="727" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C727" s="4"/>
+      <c r="O727" s="4"/>
+    </row>
+    <row r="728" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C728" s="4"/>
+      <c r="O728" s="4"/>
+    </row>
+    <row r="729" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C729" s="4"/>
+      <c r="O729" s="4"/>
+    </row>
+    <row r="730" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C730" s="4"/>
+      <c r="O730" s="4"/>
+    </row>
+    <row r="731" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C731" s="4"/>
+      <c r="O731" s="4"/>
+    </row>
+    <row r="732" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C732" s="4"/>
+      <c r="O732" s="4"/>
+    </row>
+    <row r="733" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C733" s="4"/>
+      <c r="O733" s="4"/>
+    </row>
+    <row r="734" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C734" s="4"/>
+      <c r="O734" s="4"/>
+    </row>
+    <row r="735" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C735" s="4"/>
+      <c r="O735" s="4"/>
+    </row>
+    <row r="736" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C736" s="4"/>
+      <c r="O736" s="4"/>
+    </row>
+    <row r="737" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C737" s="4"/>
+      <c r="O737" s="4"/>
+    </row>
+    <row r="738" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C738" s="4"/>
+      <c r="O738" s="4"/>
+    </row>
+    <row r="739" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C739" s="4"/>
+      <c r="O739" s="4"/>
+    </row>
+    <row r="740" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C740" s="4"/>
+      <c r="O740" s="4"/>
+    </row>
+    <row r="741" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C741" s="4"/>
+      <c r="O741" s="4"/>
+    </row>
+    <row r="742" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C742" s="4"/>
+      <c r="O742" s="4"/>
+    </row>
+    <row r="743" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C743" s="4"/>
+      <c r="O743" s="4"/>
+    </row>
+    <row r="744" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C744" s="4"/>
+      <c r="O744" s="4"/>
+    </row>
+    <row r="745" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C745" s="4"/>
+      <c r="O745" s="4"/>
+    </row>
+    <row r="746" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C746" s="4"/>
+      <c r="O746" s="4"/>
+    </row>
+    <row r="747" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C747" s="4"/>
+      <c r="O747" s="4"/>
+    </row>
+    <row r="748" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C748" s="4"/>
+      <c r="O748" s="4"/>
+    </row>
+    <row r="749" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C749" s="4"/>
+      <c r="O749" s="4"/>
+    </row>
+    <row r="750" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C750" s="4"/>
+      <c r="O750" s="4"/>
+    </row>
+    <row r="751" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C751" s="4"/>
+      <c r="O751" s="4"/>
+    </row>
+    <row r="752" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C752" s="4"/>
+      <c r="O752" s="4"/>
+    </row>
+    <row r="753" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C753" s="4"/>
+      <c r="O753" s="4"/>
+    </row>
+    <row r="754" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C754" s="4"/>
+      <c r="O754" s="4"/>
+    </row>
+    <row r="755" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C755" s="4"/>
+      <c r="O755" s="4"/>
+    </row>
+    <row r="756" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C756" s="4"/>
+      <c r="O756" s="4"/>
+    </row>
+    <row r="757" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C757" s="4"/>
+      <c r="O757" s="4"/>
+    </row>
+    <row r="758" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C758" s="4"/>
+      <c r="O758" s="4"/>
+    </row>
+    <row r="759" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C759" s="4"/>
+      <c r="O759" s="4"/>
+    </row>
+    <row r="760" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C760" s="4"/>
+      <c r="O760" s="4"/>
+    </row>
+    <row r="761" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C761" s="4"/>
+      <c r="O761" s="4"/>
+    </row>
+    <row r="762" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C762" s="4"/>
+      <c r="O762" s="4"/>
+    </row>
+    <row r="763" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C763" s="4"/>
+      <c r="O763" s="4"/>
+    </row>
+    <row r="764" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C764" s="4"/>
+      <c r="O764" s="4"/>
+    </row>
+    <row r="765" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C765" s="4"/>
+      <c r="O765" s="4"/>
+    </row>
+    <row r="766" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C766" s="4"/>
+      <c r="O766" s="4"/>
+    </row>
+    <row r="767" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C767" s="4"/>
+      <c r="O767" s="4"/>
+    </row>
+    <row r="768" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C768" s="4"/>
+      <c r="O768" s="4"/>
+    </row>
+    <row r="769" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C769" s="4"/>
+      <c r="O769" s="4"/>
+    </row>
+    <row r="770" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C770" s="4"/>
+      <c r="O770" s="4"/>
+    </row>
+    <row r="771" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C771" s="4"/>
+      <c r="O771" s="4"/>
+    </row>
+    <row r="772" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C772" s="4"/>
+      <c r="O772" s="4"/>
+    </row>
+    <row r="773" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C773" s="4"/>
+      <c r="O773" s="4"/>
+    </row>
+    <row r="774" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C774" s="4"/>
+      <c r="O774" s="4"/>
+    </row>
+    <row r="775" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C775" s="4"/>
+      <c r="O775" s="4"/>
+    </row>
+    <row r="776" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C776" s="4"/>
+      <c r="O776" s="4"/>
+    </row>
+    <row r="777" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C777" s="4"/>
+      <c r="O777" s="4"/>
+    </row>
+    <row r="778" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C778" s="4"/>
+      <c r="O778" s="4"/>
+    </row>
+    <row r="779" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C779" s="4"/>
+      <c r="O779" s="4"/>
+    </row>
+    <row r="780" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C780" s="4"/>
+      <c r="O780" s="4"/>
+    </row>
+    <row r="781" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C781" s="4"/>
+      <c r="O781" s="4"/>
+    </row>
+    <row r="782" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C782" s="4"/>
+      <c r="O782" s="4"/>
+    </row>
+    <row r="783" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C783" s="4"/>
+      <c r="O783" s="4"/>
+    </row>
+    <row r="784" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C784" s="4"/>
+      <c r="O784" s="4"/>
+    </row>
+    <row r="785" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C785" s="4"/>
+      <c r="O785" s="4"/>
+    </row>
+    <row r="786" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C786" s="4"/>
+      <c r="O786" s="4"/>
+    </row>
+    <row r="787" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C787" s="4"/>
+      <c r="O787" s="4"/>
+    </row>
+    <row r="788" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C788" s="4"/>
+      <c r="O788" s="4"/>
+    </row>
+    <row r="789" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C789" s="4"/>
+      <c r="O789" s="4"/>
+    </row>
+    <row r="790" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C790" s="4"/>
+      <c r="O790" s="4"/>
+    </row>
+    <row r="791" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C791" s="4"/>
+      <c r="O791" s="4"/>
+    </row>
+    <row r="792" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C792" s="4"/>
+      <c r="O792" s="4"/>
+    </row>
+    <row r="793" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C793" s="4"/>
+      <c r="O793" s="4"/>
+    </row>
+    <row r="794" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C794" s="4"/>
+      <c r="O794" s="4"/>
+    </row>
+    <row r="795" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C795" s="4"/>
+      <c r="O795" s="4"/>
+    </row>
+    <row r="796" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C796" s="4"/>
+      <c r="O796" s="4"/>
+    </row>
+    <row r="797" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C797" s="4"/>
+      <c r="O797" s="4"/>
+    </row>
+    <row r="798" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C798" s="4"/>
+      <c r="O798" s="4"/>
+    </row>
+    <row r="799" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C799" s="4"/>
+      <c r="O799" s="4"/>
+    </row>
+    <row r="800" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C800" s="4"/>
+      <c r="O800" s="4"/>
+    </row>
+    <row r="801" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C801" s="4"/>
+      <c r="O801" s="4"/>
+    </row>
+    <row r="802" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C802" s="4"/>
+      <c r="O802" s="4"/>
+    </row>
+    <row r="803" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C803" s="4"/>
+      <c r="O803" s="4"/>
+    </row>
+    <row r="804" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C804" s="4"/>
+      <c r="O804" s="4"/>
+    </row>
+    <row r="805" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C805" s="4"/>
+      <c r="O805" s="4"/>
+    </row>
+    <row r="806" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C806" s="4"/>
+      <c r="O806" s="4"/>
+    </row>
+    <row r="807" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C807" s="4"/>
+      <c r="O807" s="4"/>
+    </row>
+    <row r="808" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C808" s="4"/>
+      <c r="O808" s="4"/>
+    </row>
+    <row r="809" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C809" s="4"/>
+      <c r="O809" s="4"/>
+    </row>
+    <row r="810" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C810" s="4"/>
+      <c r="O810" s="4"/>
+    </row>
+    <row r="811" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C811" s="4"/>
+      <c r="O811" s="4"/>
+    </row>
+    <row r="812" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C812" s="4"/>
+      <c r="O812" s="4"/>
+    </row>
+    <row r="813" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C813" s="4"/>
+      <c r="O813" s="4"/>
+    </row>
+    <row r="814" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C814" s="4"/>
+      <c r="O814" s="4"/>
+    </row>
+    <row r="815" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C815" s="4"/>
+      <c r="O815" s="4"/>
+    </row>
+    <row r="816" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C816" s="4"/>
+      <c r="O816" s="4"/>
+    </row>
+    <row r="817" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C817" s="4"/>
+      <c r="O817" s="4"/>
+    </row>
+    <row r="818" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C818" s="4"/>
+      <c r="O818" s="4"/>
+    </row>
+    <row r="819" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C819" s="4"/>
+      <c r="O819" s="4"/>
+    </row>
+    <row r="820" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C820" s="4"/>
+      <c r="O820" s="4"/>
+    </row>
+    <row r="821" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C821" s="4"/>
+      <c r="O821" s="4"/>
+    </row>
+    <row r="822" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C822" s="4"/>
+      <c r="O822" s="4"/>
+    </row>
+    <row r="823" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C823" s="4"/>
+      <c r="O823" s="4"/>
+    </row>
+    <row r="824" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C824" s="4"/>
+      <c r="O824" s="4"/>
+    </row>
+    <row r="825" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C825" s="4"/>
+      <c r="O825" s="4"/>
+    </row>
+    <row r="826" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C826" s="4"/>
+      <c r="O826" s="4"/>
+    </row>
+    <row r="827" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C827" s="4"/>
+      <c r="O827" s="4"/>
+    </row>
+    <row r="828" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C828" s="4"/>
+      <c r="O828" s="4"/>
+    </row>
+    <row r="829" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C829" s="4"/>
+      <c r="O829" s="4"/>
+    </row>
+    <row r="830" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C830" s="4"/>
+      <c r="O830" s="4"/>
+    </row>
+    <row r="831" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C831" s="4"/>
+      <c r="O831" s="4"/>
+    </row>
+    <row r="832" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C832" s="4"/>
+      <c r="O832" s="4"/>
+    </row>
+    <row r="833" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C833" s="4"/>
+      <c r="O833" s="4"/>
+    </row>
+    <row r="834" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C834" s="4"/>
+      <c r="O834" s="4"/>
+    </row>
+    <row r="835" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C835" s="4"/>
+      <c r="O835" s="4"/>
+    </row>
+    <row r="836" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C836" s="4"/>
+      <c r="O836" s="4"/>
+    </row>
+    <row r="837" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C837" s="4"/>
+      <c r="O837" s="4"/>
+    </row>
+    <row r="838" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C838" s="4"/>
+      <c r="O838" s="4"/>
+    </row>
+    <row r="839" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C839" s="4"/>
+      <c r="O839" s="4"/>
+    </row>
+    <row r="840" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C840" s="4"/>
+      <c r="O840" s="4"/>
+    </row>
+    <row r="841" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C841" s="4"/>
+      <c r="O841" s="4"/>
+    </row>
+    <row r="842" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C842" s="4"/>
+      <c r="O842" s="4"/>
+    </row>
+    <row r="843" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C843" s="4"/>
+      <c r="O843" s="4"/>
+    </row>
+    <row r="844" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C844" s="4"/>
+      <c r="O844" s="4"/>
+    </row>
+    <row r="845" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C845" s="4"/>
+      <c r="O845" s="4"/>
+    </row>
+    <row r="846" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C846" s="4"/>
+      <c r="O846" s="4"/>
+    </row>
+    <row r="847" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C847" s="4"/>
+      <c r="O847" s="4"/>
+    </row>
+    <row r="848" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C848" s="4"/>
+      <c r="O848" s="4"/>
+    </row>
+    <row r="849" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C849" s="4"/>
+      <c r="O849" s="4"/>
+    </row>
+    <row r="850" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C850" s="4"/>
+      <c r="O850" s="4"/>
+    </row>
+    <row r="851" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C851" s="4"/>
+      <c r="O851" s="4"/>
+    </row>
+    <row r="852" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C852" s="4"/>
+      <c r="O852" s="4"/>
+    </row>
+    <row r="853" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C853" s="4"/>
+      <c r="O853" s="4"/>
+    </row>
+    <row r="854" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C854" s="4"/>
+      <c r="O854" s="4"/>
+    </row>
+    <row r="855" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C855" s="4"/>
+      <c r="O855" s="4"/>
+    </row>
+    <row r="856" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C856" s="4"/>
+      <c r="O856" s="4"/>
+    </row>
+    <row r="857" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C857" s="4"/>
+      <c r="O857" s="4"/>
+    </row>
+    <row r="858" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C858" s="4"/>
+      <c r="O858" s="4"/>
+    </row>
+    <row r="859" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C859" s="4"/>
+      <c r="O859" s="4"/>
+    </row>
+    <row r="860" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C860" s="4"/>
+      <c r="O860" s="4"/>
+    </row>
+    <row r="861" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C861" s="4"/>
+      <c r="O861" s="4"/>
+    </row>
+    <row r="862" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C862" s="4"/>
+      <c r="O862" s="4"/>
+    </row>
+    <row r="863" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C863" s="4"/>
+      <c r="O863" s="4"/>
+    </row>
+    <row r="864" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C864" s="4"/>
+      <c r="O864" s="4"/>
+    </row>
+    <row r="865" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C865" s="4"/>
+      <c r="O865" s="4"/>
+    </row>
+    <row r="866" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C866" s="4"/>
+      <c r="O866" s="4"/>
+    </row>
+    <row r="867" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C867" s="4"/>
+      <c r="O867" s="4"/>
+    </row>
+    <row r="868" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C868" s="4"/>
+      <c r="O868" s="4"/>
+    </row>
+    <row r="869" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C869" s="4"/>
+      <c r="O869" s="4"/>
+    </row>
+    <row r="870" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C870" s="4"/>
+      <c r="O870" s="4"/>
+    </row>
+    <row r="871" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C871" s="4"/>
+      <c r="O871" s="4"/>
+    </row>
+    <row r="872" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C872" s="4"/>
+      <c r="O872" s="4"/>
+    </row>
+    <row r="873" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C873" s="4"/>
+      <c r="O873" s="4"/>
+    </row>
+    <row r="874" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C874" s="4"/>
+      <c r="O874" s="4"/>
+    </row>
+    <row r="875" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C875" s="4"/>
+      <c r="O875" s="4"/>
+    </row>
+    <row r="876" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C876" s="4"/>
+      <c r="O876" s="4"/>
+    </row>
+    <row r="877" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C877" s="4"/>
+      <c r="O877" s="4"/>
+    </row>
+    <row r="878" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C878" s="4"/>
+      <c r="O878" s="4"/>
+    </row>
+    <row r="879" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C879" s="4"/>
+      <c r="O879" s="4"/>
+    </row>
+    <row r="880" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C880" s="4"/>
+      <c r="O880" s="4"/>
+    </row>
+    <row r="881" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C881" s="4"/>
+      <c r="O881" s="4"/>
+    </row>
+    <row r="882" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C882" s="4"/>
+      <c r="O882" s="4"/>
+    </row>
+    <row r="883" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C883" s="4"/>
+      <c r="O883" s="4"/>
+    </row>
+    <row r="884" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C884" s="4"/>
+      <c r="O884" s="4"/>
+    </row>
+    <row r="885" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C885" s="4"/>
+      <c r="O885" s="4"/>
+    </row>
+    <row r="886" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C886" s="4"/>
+      <c r="O886" s="4"/>
+    </row>
+    <row r="887" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C887" s="4"/>
+      <c r="O887" s="4"/>
+    </row>
+    <row r="888" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C888" s="4"/>
+      <c r="O888" s="4"/>
+    </row>
+    <row r="889" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C889" s="4"/>
+      <c r="O889" s="4"/>
+    </row>
+    <row r="890" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C890" s="4"/>
+      <c r="O890" s="4"/>
+    </row>
+    <row r="891" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C891" s="4"/>
+      <c r="O891" s="4"/>
+    </row>
+    <row r="892" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C892" s="4"/>
+      <c r="O892" s="4"/>
+    </row>
+    <row r="893" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C893" s="4"/>
+      <c r="O893" s="4"/>
+    </row>
+    <row r="894" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C894" s="4"/>
+      <c r="O894" s="4"/>
+    </row>
+    <row r="895" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C895" s="4"/>
+      <c r="O895" s="4"/>
+    </row>
+    <row r="896" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C896" s="4"/>
+      <c r="O896" s="4"/>
+    </row>
+    <row r="897" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C897" s="4"/>
+      <c r="O897" s="4"/>
+    </row>
+    <row r="898" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C898" s="4"/>
+      <c r="O898" s="4"/>
+    </row>
+    <row r="899" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C899" s="4"/>
+      <c r="O899" s="4"/>
+    </row>
+    <row r="900" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C900" s="4"/>
+      <c r="O900" s="4"/>
+    </row>
+    <row r="901" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C901" s="4"/>
+      <c r="O901" s="4"/>
+    </row>
+    <row r="902" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C902" s="4"/>
+      <c r="O902" s="4"/>
+    </row>
+    <row r="903" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C903" s="4"/>
+      <c r="O903" s="4"/>
+    </row>
+    <row r="904" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C904" s="4"/>
+      <c r="O904" s="4"/>
+    </row>
+    <row r="905" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C905" s="4"/>
+      <c r="O905" s="4"/>
+    </row>
+    <row r="906" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C906" s="4"/>
+      <c r="O906" s="4"/>
+    </row>
+    <row r="907" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C907" s="4"/>
+      <c r="O907" s="4"/>
+    </row>
+    <row r="908" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C908" s="4"/>
+      <c r="O908" s="4"/>
+    </row>
+    <row r="909" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C909" s="4"/>
+      <c r="O909" s="4"/>
+    </row>
+    <row r="910" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C910" s="4"/>
+      <c r="O910" s="4"/>
+    </row>
+    <row r="911" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C911" s="4"/>
+      <c r="O911" s="4"/>
+    </row>
+    <row r="912" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C912" s="4"/>
+      <c r="O912" s="4"/>
+    </row>
+    <row r="913" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C913" s="4"/>
+      <c r="O913" s="4"/>
+    </row>
+    <row r="914" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C914" s="4"/>
+      <c r="O914" s="4"/>
+    </row>
+    <row r="915" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C915" s="4"/>
+      <c r="O915" s="4"/>
+    </row>
+    <row r="916" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C916" s="4"/>
+      <c r="O916" s="4"/>
+    </row>
+    <row r="917" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C917" s="4"/>
+      <c r="O917" s="4"/>
+    </row>
+    <row r="918" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C918" s="4"/>
+      <c r="O918" s="4"/>
+    </row>
+    <row r="919" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C919" s="4"/>
+      <c r="O919" s="4"/>
+    </row>
+    <row r="920" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C920" s="4"/>
+      <c r="O920" s="4"/>
+    </row>
+    <row r="921" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C921" s="4"/>
+      <c r="O921" s="4"/>
+    </row>
+    <row r="922" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C922" s="4"/>
+      <c r="O922" s="4"/>
+    </row>
+    <row r="923" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C923" s="4"/>
+      <c r="O923" s="4"/>
+    </row>
+    <row r="924" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C924" s="4"/>
+      <c r="O924" s="4"/>
+    </row>
+    <row r="925" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C925" s="4"/>
+      <c r="O925" s="4"/>
+    </row>
+    <row r="926" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C926" s="4"/>
+      <c r="O926" s="4"/>
+    </row>
+    <row r="927" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C927" s="4"/>
+      <c r="O927" s="4"/>
+    </row>
+    <row r="928" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C928" s="4"/>
+      <c r="O928" s="4"/>
+    </row>
+    <row r="929" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C929" s="4"/>
+      <c r="O929" s="4"/>
+    </row>
+    <row r="930" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C930" s="4"/>
+      <c r="O930" s="4"/>
+    </row>
+    <row r="931" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C931" s="4"/>
+      <c r="O931" s="4"/>
+    </row>
+    <row r="932" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C932" s="4"/>
+      <c r="O932" s="4"/>
+    </row>
+    <row r="933" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C933" s="4"/>
+      <c r="O933" s="4"/>
+    </row>
+    <row r="934" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C934" s="4"/>
+      <c r="O934" s="4"/>
+    </row>
+    <row r="935" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C935" s="4"/>
+      <c r="O935" s="4"/>
+    </row>
+    <row r="936" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C936" s="4"/>
+      <c r="O936" s="4"/>
+    </row>
+    <row r="937" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C937" s="4"/>
+      <c r="O937" s="4"/>
+    </row>
+    <row r="938" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C938" s="4"/>
+      <c r="O938" s="4"/>
+    </row>
+    <row r="939" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C939" s="4"/>
+      <c r="O939" s="4"/>
+    </row>
+    <row r="940" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C940" s="4"/>
+      <c r="O940" s="4"/>
+    </row>
+    <row r="941" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C941" s="4"/>
+      <c r="O941" s="4"/>
+    </row>
+    <row r="942" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C942" s="4"/>
+      <c r="O942" s="4"/>
+    </row>
+    <row r="943" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C943" s="4"/>
+      <c r="O943" s="4"/>
+    </row>
+    <row r="944" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C944" s="4"/>
+      <c r="O944" s="4"/>
+    </row>
+    <row r="945" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C945" s="4"/>
+      <c r="O945" s="4"/>
+    </row>
+    <row r="946" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C946" s="4"/>
+      <c r="O946" s="4"/>
+    </row>
+    <row r="947" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C947" s="4"/>
+      <c r="O947" s="4"/>
+    </row>
+    <row r="948" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C948" s="4"/>
+      <c r="O948" s="4"/>
+    </row>
+    <row r="949" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C949" s="4"/>
+      <c r="O949" s="4"/>
+    </row>
+    <row r="950" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C950" s="4"/>
+      <c r="O950" s="4"/>
+    </row>
+    <row r="951" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C951" s="4"/>
+      <c r="O951" s="4"/>
+    </row>
+    <row r="952" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C952" s="4"/>
+      <c r="O952" s="4"/>
+    </row>
+    <row r="953" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C953" s="4"/>
+      <c r="O953" s="4"/>
+    </row>
+    <row r="954" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C954" s="4"/>
+      <c r="O954" s="4"/>
+    </row>
+    <row r="955" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C955" s="4"/>
+      <c r="O955" s="4"/>
+    </row>
+    <row r="956" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C956" s="4"/>
+      <c r="O956" s="4"/>
+    </row>
+    <row r="957" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C957" s="4"/>
+      <c r="O957" s="4"/>
+    </row>
+    <row r="958" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C958" s="4"/>
+      <c r="O958" s="4"/>
+    </row>
+    <row r="959" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C959" s="4"/>
+      <c r="O959" s="4"/>
+    </row>
+    <row r="960" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C960" s="4"/>
+      <c r="O960" s="4"/>
+    </row>
+    <row r="961" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C961" s="4"/>
+      <c r="O961" s="4"/>
+    </row>
+    <row r="962" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C962" s="4"/>
+      <c r="O962" s="4"/>
+    </row>
+    <row r="963" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C963" s="4"/>
+      <c r="O963" s="4"/>
+    </row>
+    <row r="964" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C964" s="4"/>
+      <c r="O964" s="4"/>
+    </row>
+    <row r="965" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C965" s="4"/>
+      <c r="O965" s="4"/>
+    </row>
+    <row r="966" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C966" s="4"/>
+      <c r="O966" s="4"/>
+    </row>
+    <row r="967" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C967" s="4"/>
+      <c r="O967" s="4"/>
+    </row>
+    <row r="968" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C968" s="4"/>
+      <c r="O968" s="4"/>
+    </row>
+    <row r="969" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C969" s="4"/>
+      <c r="O969" s="4"/>
+    </row>
+    <row r="970" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C970" s="4"/>
+      <c r="O970" s="4"/>
+    </row>
+    <row r="971" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C971" s="4"/>
+      <c r="O971" s="4"/>
+    </row>
+    <row r="972" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C972" s="4"/>
+      <c r="O972" s="4"/>
+    </row>
+    <row r="973" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C973" s="4"/>
+      <c r="O973" s="4"/>
+    </row>
+    <row r="974" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C974" s="4"/>
+      <c r="O974" s="4"/>
+    </row>
+    <row r="975" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C975" s="4"/>
+      <c r="O975" s="4"/>
+    </row>
+    <row r="976" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C976" s="4"/>
+      <c r="O976" s="4"/>
+    </row>
+    <row r="977" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C977" s="4"/>
+      <c r="O977" s="4"/>
+    </row>
+    <row r="978" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C978" s="4"/>
+      <c r="O978" s="4"/>
+    </row>
+    <row r="979" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C979" s="4"/>
+      <c r="O979" s="4"/>
+    </row>
+    <row r="980" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C980" s="4"/>
+      <c r="O980" s="4"/>
+    </row>
+    <row r="981" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C981" s="4"/>
+      <c r="O981" s="4"/>
+    </row>
+    <row r="982" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C982" s="4"/>
+      <c r="O982" s="4"/>
+    </row>
+    <row r="983" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C983" s="4"/>
+      <c r="O983" s="4"/>
+    </row>
+    <row r="984" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C984" s="4"/>
+      <c r="O984" s="4"/>
+    </row>
+    <row r="985" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C985" s="4"/>
+      <c r="O985" s="4"/>
+    </row>
+    <row r="986" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C986" s="4"/>
+      <c r="O986" s="4"/>
+    </row>
+    <row r="987" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C987" s="4"/>
+      <c r="O987" s="4"/>
+    </row>
+    <row r="988" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C988" s="4"/>
+      <c r="O988" s="4"/>
+    </row>
+    <row r="989" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C989" s="4"/>
+      <c r="O989" s="4"/>
+    </row>
+    <row r="990" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C990" s="4"/>
+      <c r="O990" s="4"/>
+    </row>
+    <row r="991" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C991" s="4"/>
+      <c r="O991" s="4"/>
+    </row>
+    <row r="992" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C992" s="4"/>
+      <c r="O992" s="4"/>
+    </row>
+    <row r="993" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C993" s="4"/>
+      <c r="O993" s="4"/>
+    </row>
+    <row r="994" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C994" s="4"/>
+      <c r="O994" s="4"/>
+    </row>
+    <row r="995" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C995" s="4"/>
+      <c r="O995" s="4"/>
+    </row>
+    <row r="996" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C996" s="4"/>
+      <c r="O996" s="4"/>
+    </row>
+    <row r="997" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C997" s="4"/>
+      <c r="O997" s="4"/>
+    </row>
+    <row r="998" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C998" s="4"/>
+      <c r="O998" s="4"/>
+    </row>
+    <row r="999" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C999" s="4"/>
+      <c r="O999" s="4"/>
+    </row>
+    <row r="1000" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1000" s="4"/>
+      <c r="O1000" s="4"/>
+    </row>
+    <row r="1001" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1001" s="4"/>
+      <c r="O1001" s="4"/>
+    </row>
+    <row r="1002" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1002" s="4"/>
+      <c r="O1002" s="4"/>
+    </row>
+    <row r="1003" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1003" s="4"/>
+      <c r="O1003" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2:L1003" type="list">
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N1003" type="list">
       <formula1>"Accounting,Reporting"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C1:C1003" type="list">
+      <formula1>"Founder,Employee,Other,Self"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O1:O1003" type="list">
+      <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
